--- a/data/trans_orig/P1416-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2007</t>
+          <t>Población con diagnóstico de alergias crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22711</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248198</t>
+          <t>248342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264496</t>
+          <t>264609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238127</t>
+          <t>238742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253687</t>
+          <t>253395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493134</t>
+          <t>493149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>513685</t>
+          <t>514451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45722</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>67974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103434</t>
+          <t>105135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>447353</t>
+          <t>448543</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470531</t>
+          <t>471109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>435975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463149</t>
+          <t>463016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>893590</t>
+          <t>891889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928978</t>
+          <t>928552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>34347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>51929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295743</t>
+          <t>296402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310666</t>
+          <t>311639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301395</t>
+          <t>301065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319674</t>
+          <t>320231</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602862</t>
+          <t>602329</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627863</t>
+          <t>627618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>20684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41825</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56263</t>
+          <t>54758</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>57887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92465</t>
+          <t>91340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>316846</t>
+          <t>315041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337931</t>
+          <t>337987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315193</t>
+          <t>316698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339496</t>
+          <t>340235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>637662</t>
+          <t>638787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>671924</t>
+          <t>672240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31869</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58788</t>
+          <t>57888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175262</t>
+          <t>175915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192762</t>
+          <t>192724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170136</t>
+          <t>170320</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190193</t>
+          <t>189307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>352188</t>
+          <t>353088</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379107</t>
+          <t>379243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16929</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>54714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246474</t>
+          <t>245353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262070</t>
+          <t>262173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242213</t>
+          <t>242647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261215</t>
+          <t>261221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>496315</t>
+          <t>494241</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520016</t>
+          <t>519766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>37560</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31130</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>54057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>52733</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85607</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>576612</t>
+          <t>577467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597003</t>
+          <t>598072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584092</t>
+          <t>584162</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>607089</t>
+          <t>608227</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1167639</t>
+          <t>1168151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199648</t>
+          <t>1200513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54065</t>
+          <t>54965</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84300</t>
+          <t>85468</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79964</t>
+          <t>81687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117435</t>
+          <t>118379</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145607</t>
+          <t>142859</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>192987</t>
+          <t>191548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>659495</t>
+          <t>658327</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>689730</t>
+          <t>688830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>666076</t>
+          <t>665132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>703547</t>
+          <t>701824</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1334319</t>
+          <t>1335758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1381699</t>
+          <t>1384447</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193186</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>253999</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>289998</t>
+          <t>290318</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>360635</t>
+          <t>357888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>498737</t>
+          <t>501629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>587273</t>
+          <t>590728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3022544</t>
+          <t>3026634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3081834</t>
+          <t>3083357</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3018562</t>
+          <t>3021309</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3089199</t>
+          <t>3088879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6068468</t>
+          <t>6065013</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6157004</t>
+          <t>6154112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2012</t>
+          <t>Población con diagnóstico de alergias crónicas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31486</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44705</t>
+          <t>44529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>40790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>69088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263252</t>
+          <t>264137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280614</t>
+          <t>281610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242540</t>
+          <t>242716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266084</t>
+          <t>266189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512310</t>
+          <t>512895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>541193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44348</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26810</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51828</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52061</t>
+          <t>51396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85967</t>
+          <t>86628</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461179</t>
+          <t>460018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485757</t>
+          <t>485176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471937</t>
+          <t>470678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496955</t>
+          <t>497200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>943325</t>
+          <t>942664</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977231</t>
+          <t>977896</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>39426</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54714</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>302174</t>
+          <t>301699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317117</t>
+          <t>317086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301669</t>
+          <t>301594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322691</t>
+          <t>323059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610352</t>
+          <t>611334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635638</t>
+          <t>636796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26239</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>33389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>60528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>346532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364454</t>
+          <t>363797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346306</t>
+          <t>345977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369638</t>
+          <t>368407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700850</t>
+          <t>702405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728662</t>
+          <t>729544</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55451</t>
+          <t>56014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187678</t>
+          <t>187441</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202657</t>
+          <t>203345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183371</t>
+          <t>181806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201757</t>
+          <t>201267</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376758</t>
+          <t>376195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>401467</t>
+          <t>400206</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>25379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>21938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248410</t>
+          <t>248646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265242</t>
+          <t>265069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254229</t>
+          <t>254652</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270798</t>
+          <t>270770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>509976</t>
+          <t>507882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532134</t>
+          <t>532074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52780</t>
+          <t>53621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46927</t>
+          <t>47995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80794</t>
+          <t>79218</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>628533</t>
+          <t>628951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>647741</t>
+          <t>648306</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>641073</t>
+          <t>640232</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>666561</t>
+          <t>666859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275847</t>
+          <t>1277423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1309714</t>
+          <t>1308646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>28236</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53238</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40114</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>68263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75943</t>
+          <t>75088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>113223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>724838</t>
+          <t>724608</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>749470</t>
+          <t>749840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755858</t>
+          <t>754315</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>782464</t>
+          <t>783084</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1486502</t>
+          <t>1487431</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1524711</t>
+          <t>1525566</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152076</t>
+          <t>150737</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>206038</t>
+          <t>203071</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>229317</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>293579</t>
+          <t>293884</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>397343</t>
+          <t>398486</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>480849</t>
+          <t>481127</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3219719</t>
+          <t>3222686</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3273681</t>
+          <t>3275020</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3263455</t>
+          <t>3263150</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3332095</t>
+          <t>3327717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6501941</t>
+          <t>6501663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6585447</t>
+          <t>6584304</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2016</t>
+          <t>Población con diagnóstico de alergias crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29999</t>
+          <t>27803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60375</t>
+          <t>61443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263762</t>
+          <t>265958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282288</t>
+          <t>282818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250555</t>
+          <t>249333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270948</t>
+          <t>269904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>522089</t>
+          <t>521021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>548939</t>
+          <t>550367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>29646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26594</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72163</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474117</t>
+          <t>472929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491266</t>
+          <t>491518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471627</t>
+          <t>471408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496490</t>
+          <t>494701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953496</t>
+          <t>954192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983007</t>
+          <t>983532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22163</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8350</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22232</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18650</t>
+          <t>19111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296402</t>
+          <t>296826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310775</t>
+          <t>311094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327959</t>
+          <t>328929</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>617023</t>
+          <t>615797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636224</t>
+          <t>635763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>32077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>24989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48435</t>
+          <t>47869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>41336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70569</t>
+          <t>71146</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339356</t>
+          <t>337887</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358702</t>
+          <t>357916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338848</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362380</t>
+          <t>362294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>686678</t>
+          <t>686101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716727</t>
+          <t>715911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42021</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191411</t>
+          <t>191770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205086</t>
+          <t>205043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190437</t>
+          <t>191350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>206916</t>
+          <t>207318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387787</t>
+          <t>387576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408814</t>
+          <t>409412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>25971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>29928</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25580</t>
+          <t>25831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48939</t>
+          <t>49122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237785</t>
+          <t>237152</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253232</t>
+          <t>252741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242742</t>
+          <t>243187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260592</t>
+          <t>260838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487299</t>
+          <t>487116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510658</t>
+          <t>510407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>10938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39510</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>68146</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57845</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>90911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>626250</t>
+          <t>625898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644688</t>
+          <t>645620</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623559</t>
+          <t>623148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651666</t>
+          <t>651784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1254606</t>
+          <t>1256941</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1290007</t>
+          <t>1292301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>64027</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61398</t>
+          <t>61761</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94555</t>
+          <t>97035</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>105145</t>
+          <t>106724</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>150407</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>713335</t>
+          <t>714556</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>741999</t>
+          <t>741610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731612</t>
+          <t>729132</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>764769</t>
+          <t>764406</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1455137</t>
+          <t>1454343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1499605</t>
+          <t>1498026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>144483</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>196124</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>242891</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316062</t>
+          <t>311813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>410259</t>
+          <t>409329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>499273</t>
+          <t>495829</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3199430</t>
+          <t>3198226</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3249867</t>
+          <t>3251668</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3228480</t>
+          <t>3232729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3293876</t>
+          <t>3301651</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6439619</t>
+          <t>6443063</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6528633</t>
+          <t>6529563</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2023</t>
+          <t>Población con diagnóstico de alergias crónicas en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69033</t>
+          <t>66679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39399</t>
+          <t>39352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85099</t>
+          <t>85307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242410</t>
+          <t>244764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284568</t>
+          <t>284767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>268451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280065</t>
+          <t>280168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515978</t>
+          <t>515770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>561725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46264</t>
+          <t>46057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88614</t>
+          <t>89683</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53006</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80378</t>
+          <t>80179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108000</t>
+          <t>107772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157862</t>
+          <t>158197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428779</t>
+          <t>427710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471129</t>
+          <t>471336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429380</t>
+          <t>429579</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456752</t>
+          <t>456816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>869289</t>
+          <t>868954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919151</t>
+          <t>919379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40677</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>27502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48023</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79872</t>
+          <t>79740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275373</t>
+          <t>275243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297176</t>
+          <t>295779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301105</t>
+          <t>300732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321363</t>
+          <t>321626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585306</t>
+          <t>585438</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613804</t>
+          <t>613186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8929</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30888</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>23159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53199</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282165</t>
+          <t>280396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>303628</t>
+          <t>304365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444830</t>
+          <t>443359</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463916</t>
+          <t>463965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>735075</t>
+          <t>734930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>765113</t>
+          <t>765115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32441</t>
+          <t>32722</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>54997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151875</t>
+          <t>150704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166866</t>
+          <t>166316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175144</t>
+          <t>174863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188803</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332743</t>
+          <t>331330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352802</t>
+          <t>351498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>49965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36038</t>
+          <t>35923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69626</t>
+          <t>68471</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98819</t>
+          <t>98344</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219560</t>
+          <t>218811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241687</t>
+          <t>240986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201354</t>
+          <t>200297</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220349</t>
+          <t>220464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426343</t>
+          <t>426818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>455536</t>
+          <t>456691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89211</t>
+          <t>91006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49504</t>
+          <t>49726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149970</t>
+          <t>150893</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>117935</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219010</t>
+          <t>221040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>531272</t>
+          <t>529477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>565259</t>
+          <t>565219</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>698663</t>
+          <t>697740</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>799129</t>
+          <t>798907</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1250106</t>
+          <t>1248076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1360155</t>
+          <t>1351181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70632</t>
+          <t>72523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65568</t>
+          <t>64649</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93113</t>
+          <t>92454</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72994</t>
+          <t>70609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154494</t>
+          <t>156205</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>858088</t>
+          <t>856197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>908540</t>
+          <t>909167</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>613875</t>
+          <t>614534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641420</t>
+          <t>642339</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1481215</t>
+          <t>1479504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1562715</t>
+          <t>1565100</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>251169</t>
+          <t>255310</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>374599</t>
+          <t>379206</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>313196</t>
+          <t>320292</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>434456</t>
+          <t>440376</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>626449</t>
+          <t>623311</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>791239</t>
+          <t>790962</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3079565</t>
+          <t>3074958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3202995</t>
+          <t>3198854</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3209376</t>
+          <t>3203456</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3330636</t>
+          <t>3323540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6306757</t>
+          <t>6307034</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6471547</t>
+          <t>6474685</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1416-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22096</t>
+          <t>22001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248342</t>
+          <t>249102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264609</t>
+          <t>263984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>238742</t>
+          <t>238837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253395</t>
+          <t>253419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493149</t>
+          <t>493486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514451</t>
+          <t>514734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>46350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>40378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68472</t>
+          <t>70636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105135</t>
+          <t>105608</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448543</t>
+          <t>446725</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471109</t>
+          <t>470552</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>435975</t>
+          <t>435742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463016</t>
+          <t>463571</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891889</t>
+          <t>891416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928552</t>
+          <t>926388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>22896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51929</t>
+          <t>51084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296402</t>
+          <t>295950</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311639</t>
+          <t>311339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301065</t>
+          <t>299985</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320231</t>
+          <t>319290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602329</t>
+          <t>603174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627618</t>
+          <t>626655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20684</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43630</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>31305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>55945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91340</t>
+          <t>90520</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315041</t>
+          <t>316105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>337987</t>
+          <t>337726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>316698</t>
+          <t>315511</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>340151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638787</t>
+          <t>639607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672240</t>
+          <t>672599</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>17419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>58083</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175915</t>
+          <t>176317</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192724</t>
+          <t>193024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170320</t>
+          <t>170273</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189307</t>
+          <t>190249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353088</t>
+          <t>352893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>379243</t>
+          <t>378648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25458</t>
+          <t>23648</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>35534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54714</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>245353</t>
+          <t>247163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262173</t>
+          <t>262274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>242647</t>
+          <t>242610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>261221</t>
+          <t>261373</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>494241</t>
+          <t>494711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519766</t>
+          <t>519482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37560</t>
+          <t>38309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>29767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54057</t>
+          <t>55569</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52733</t>
+          <t>52306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85095</t>
+          <t>83403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577467</t>
+          <t>576718</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598072</t>
+          <t>597431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>584162</t>
+          <t>582650</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>608227</t>
+          <t>608452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1168151</t>
+          <t>1169843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1200513</t>
+          <t>1200940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>53740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85468</t>
+          <t>86488</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81687</t>
+          <t>81935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118379</t>
+          <t>120426</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142859</t>
+          <t>144810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>191548</t>
+          <t>191623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>658327</t>
+          <t>657307</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>688830</t>
+          <t>690055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>665132</t>
+          <t>663085</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701824</t>
+          <t>701576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1335758</t>
+          <t>1335683</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1384447</t>
+          <t>1382496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193186</t>
+          <t>188622</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>290318</t>
+          <t>291854</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>357888</t>
+          <t>358099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>499853</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>590728</t>
+          <t>593898</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3026634</t>
+          <t>3025900</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3083357</t>
+          <t>3087921</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3021309</t>
+          <t>3021098</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3088879</t>
+          <t>3087343</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6065013</t>
+          <t>6061843</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6154112</t>
+          <t>6155888</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21056</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44529</t>
+          <t>44698</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40790</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264137</t>
+          <t>262768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281610</t>
+          <t>280839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242716</t>
+          <t>242547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266189</t>
+          <t>266023</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512895</t>
+          <t>511988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541193</t>
+          <t>541119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>43685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>50993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>54007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86628</t>
+          <t>87395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460018</t>
+          <t>461842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>485176</t>
+          <t>486768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>470678</t>
+          <t>472772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497200</t>
+          <t>497541</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>942664</t>
+          <t>941897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>977896</t>
+          <t>975285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39426</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>29193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53732</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>301699</t>
+          <t>301665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317086</t>
+          <t>317132</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301594</t>
+          <t>302891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323059</t>
+          <t>323187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611334</t>
+          <t>610638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636796</t>
+          <t>635873</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>26215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20544</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42974</t>
+          <t>40475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33389</t>
+          <t>33767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60528</t>
+          <t>60183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346532</t>
+          <t>347767</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363797</t>
+          <t>363639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>345977</t>
+          <t>348476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368407</t>
+          <t>369350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>702405</t>
+          <t>702750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>729544</t>
+          <t>729166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56014</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187441</t>
+          <t>188257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203345</t>
+          <t>203532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181806</t>
+          <t>182411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201267</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>376195</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400206</t>
+          <t>400642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>27219</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>45577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248646</t>
+          <t>246762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265069</t>
+          <t>264730</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254652</t>
+          <t>254911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270770</t>
+          <t>271200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507882</t>
+          <t>508435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532074</t>
+          <t>532985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33837</t>
+          <t>33229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53621</t>
+          <t>53082</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>48608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>79218</t>
+          <t>79581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>628951</t>
+          <t>629559</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648306</t>
+          <t>648881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>640232</t>
+          <t>640771</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>666859</t>
+          <t>665725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277423</t>
+          <t>1277060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1308646</t>
+          <t>1308033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28236</t>
+          <t>28339</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>53423</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>40610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68263</t>
+          <t>67914</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75088</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113223</t>
+          <t>114698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>724608</t>
+          <t>724653</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>749840</t>
+          <t>749737</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>754315</t>
+          <t>754664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>783084</t>
+          <t>781968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1487431</t>
+          <t>1485956</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1525566</t>
+          <t>1525227</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>149764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>203598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>229317</t>
+          <t>230262</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>293884</t>
+          <t>293374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>398486</t>
+          <t>398827</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>481127</t>
+          <t>481472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3222686</t>
+          <t>3222159</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3275020</t>
+          <t>3275993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3263150</t>
+          <t>3263660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3327717</t>
+          <t>3326772</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6501663</t>
+          <t>6501318</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6584304</t>
+          <t>6583963</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27803</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39370</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>33879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>61413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265958</t>
+          <t>264788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282818</t>
+          <t>283290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249333</t>
+          <t>248813</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269904</t>
+          <t>270731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521021</t>
+          <t>521051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>550367</t>
+          <t>548585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29646</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28383</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51676</t>
+          <t>53244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42127</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>74446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472929</t>
+          <t>474577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491518</t>
+          <t>491399</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471408</t>
+          <t>469840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>494701</t>
+          <t>494768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>954192</t>
+          <t>951213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>983532</t>
+          <t>981750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>21925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>18966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>38609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296826</t>
+          <t>296741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>311094</t>
+          <t>310258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314794</t>
+          <t>314384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328929</t>
+          <t>328070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615797</t>
+          <t>616265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635763</t>
+          <t>635908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32077</t>
+          <t>30462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24989</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47869</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>40547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71146</t>
+          <t>70169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>337887</t>
+          <t>339502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357916</t>
+          <t>358005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>339414</t>
+          <t>338975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362294</t>
+          <t>362080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>686101</t>
+          <t>687078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715911</t>
+          <t>716700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20396</t>
+          <t>19953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>42294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>192405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205043</t>
+          <t>205207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191350</t>
+          <t>189709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207318</t>
+          <t>206768</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387576</t>
+          <t>387514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409412</t>
+          <t>409855</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25831</t>
+          <t>25993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49122</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237152</t>
+          <t>237764</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>252741</t>
+          <t>252897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243187</t>
+          <t>242154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260838</t>
+          <t>261091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487116</t>
+          <t>486507</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510407</t>
+          <t>510245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10938</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>40022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>57251</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>90936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>625898</t>
+          <t>625857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>645620</t>
+          <t>645670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623148</t>
+          <t>622383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>651784</t>
+          <t>651272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256941</t>
+          <t>1256916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292301</t>
+          <t>1290601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>37267</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64027</t>
+          <t>65416</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61761</t>
+          <t>59775</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97035</t>
+          <t>94330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106724</t>
+          <t>106097</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150407</t>
+          <t>149108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>714556</t>
+          <t>713167</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>741610</t>
+          <t>741316</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>729132</t>
+          <t>731837</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>764406</t>
+          <t>766392</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1454343</t>
+          <t>1455642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1498026</t>
+          <t>1498653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>143896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>196124</t>
+          <t>193843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>242891</t>
+          <t>250472</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>311813</t>
+          <t>315818</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>409329</t>
+          <t>408350</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>493309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3198226</t>
+          <t>3200507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3251668</t>
+          <t>3250454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3232729</t>
+          <t>3228724</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3301651</t>
+          <t>3294070</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6443063</t>
+          <t>6445583</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6529563</t>
+          <t>6530542</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>22569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>48905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>51820</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85307</t>
+          <t>68069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>269196</t>
+          <t>285720</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244764</t>
+          <t>269940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284767</t>
+          <t>296276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>275241</t>
+          <t>297366</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268451</t>
+          <t>287254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280168</t>
+          <t>303219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>544436</t>
+          <t>583086</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515770</t>
+          <t>566837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>561725</t>
+          <t>596611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89683</t>
+          <t>86329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65456</t>
+          <t>68251</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>54677</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80179</t>
+          <t>83415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>133025</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107772</t>
+          <t>110076</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>158197</t>
+          <t>161752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>452860</t>
+          <t>464886</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>427710</t>
+          <t>443331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471336</t>
+          <t>481179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>444302</t>
+          <t>472917</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>429579</t>
+          <t>457753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456816</t>
+          <t>486491</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>897162</t>
+          <t>937803</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>868954</t>
+          <t>909076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919379</t>
+          <t>960752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>509758</t>
+          <t>541168</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>509758</t>
+          <t>541168</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>509758</t>
+          <t>541168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1027151</t>
+          <t>1070828</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1027151</t>
+          <t>1070828</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1027151</t>
+          <t>1070828</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40807</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48396</t>
+          <t>47111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>65270</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51992</t>
+          <t>52540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79740</t>
+          <t>80373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>287470</t>
+          <t>287137</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275243</t>
+          <t>274573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>295779</t>
+          <t>295931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>312874</t>
+          <t>319967</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300732</t>
+          <t>309270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>321626</t>
+          <t>328953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>600344</t>
+          <t>607105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585438</t>
+          <t>592002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613186</t>
+          <t>619835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,22 +11726,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32161</t>
+          <t>37196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32359</t>
+          <t>34565</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>41583</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>29587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>61119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -11839,27 +11839,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>296427</t>
+          <t>355248</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280396</t>
+          <t>335949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304365</t>
+          <t>363387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>455180</t>
+          <t>398276</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443359</t>
+          <t>387396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>463965</t>
+          <t>405889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>751606</t>
+          <t>753524</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>734930</t>
+          <t>733988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>765115</t>
+          <t>765520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32722</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43315</t>
+          <t>45884</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>36517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54997</t>
+          <t>57024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160233</t>
+          <t>185888</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150704</t>
+          <t>176100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166316</t>
+          <t>192520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>182779</t>
+          <t>200029</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174863</t>
+          <t>192449</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189032</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>343012</t>
+          <t>385916</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>331330</t>
+          <t>374776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351498</t>
+          <t>395283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>226136</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386327</t>
+          <t>431800</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386327</t>
+          <t>431800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386327</t>
+          <t>431800</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27790</t>
+          <t>27582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49965</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>37336</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56090</t>
+          <t>57069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>82534</t>
+          <t>84712</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68471</t>
+          <t>70152</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98344</t>
+          <t>98744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>232306</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218811</t>
+          <t>221338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240986</t>
+          <t>242313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>211270</t>
+          <t>215976</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>200297</t>
+          <t>206030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>220464</t>
+          <t>225763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>442628</t>
+          <t>448283</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426818</t>
+          <t>434251</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>456691</t>
+          <t>462843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268776</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268776</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268776</t>
+          <t>269895</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525162</t>
+          <t>532995</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525162</t>
+          <t>532995</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525162</t>
+          <t>532995</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>87480</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55264</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91006</t>
+          <t>110658</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>108527</t>
+          <t>133747</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>49726</t>
+          <t>114760</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150893</t>
+          <t>154702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>179686</t>
+          <t>221227</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>117935</t>
+          <t>194495</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>221040</t>
+          <t>250209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>549323</t>
+          <t>628178</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>529477</t>
+          <t>605000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>565219</t>
+          <t>644549</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>740106</t>
+          <t>637620</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>697740</t>
+          <t>616665</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>798907</t>
+          <t>656607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1289430</t>
+          <t>1265798</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1248076</t>
+          <t>1236816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351181</t>
+          <t>1292530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620483</t>
+          <t>715658</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620483</t>
+          <t>715658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620483</t>
+          <t>715658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848633</t>
+          <t>771367</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848633</t>
+          <t>771367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848633</t>
+          <t>771367</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469116</t>
+          <t>1487025</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469116</t>
+          <t>1487025</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469116</t>
+          <t>1487025</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>53430</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>39189</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72523</t>
+          <t>70320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64649</t>
+          <t>75764</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92454</t>
+          <t>106972</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>124339</t>
+          <t>144588</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70609</t>
+          <t>121145</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156205</t>
+          <t>165879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>882281</t>
+          <t>744642</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856197</t>
+          <t>727752</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>909167</t>
+          <t>758883</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>629088</t>
+          <t>730193</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>614534</t>
+          <t>714379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>642339</t>
+          <t>745587</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1511370</t>
+          <t>1474834</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1479504</t>
+          <t>1453543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1565100</t>
+          <t>1498277</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>706988</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>706988</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>706988</t>
+          <t>821351</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1635709</t>
+          <t>1619422</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1635709</t>
+          <t>1619422</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1635709</t>
+          <t>1619422</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>255310</t>
+          <t>302109</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>379206</t>
+          <t>386344</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>320292</t>
+          <t>411567</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>484539</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>623311</t>
+          <t>732522</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>790962</t>
+          <t>840964</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3129149</t>
+          <t>3184004</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3074958</t>
+          <t>3140589</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3198854</t>
+          <t>3224824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3250840</t>
+          <t>3272343</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3203456</t>
+          <t>3232986</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3323540</t>
+          <t>3305958</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6379989</t>
+          <t>6456347</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6307034</t>
+          <t>6403494</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6474685</t>
+          <t>6511936</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
